--- a/AAII_Financials/Quarterly/DHR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DHR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="92">
   <si>
     <t>DHR</t>
   </si>
@@ -656,542 +656,555 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46199</v>
+      </c>
+      <c r="E7" s="2">
         <v>46108</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45835</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45744</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45562</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45471</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45380</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45198</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44743</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44652</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44470</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44379</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44288</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44106</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44015</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43924</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43735</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43644</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43553</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43371</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43280</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43189</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43007</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>6265000</v>
+      </c>
+      <c r="E8" s="3">
         <v>5951000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>6838000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>6053000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>5936000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>5741000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>6538000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>5798000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>5743000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5796000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>6405000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>5624000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>5912000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>5949000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>26643000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>7663000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>7751000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>7688000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>8148000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>7229000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>7218000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>6858000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>6760300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>5883200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>5297400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>4343100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>4868300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>4378000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>4444500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>4220200</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2519000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>4853100</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>4981000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>4695400</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>5085700</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>4528200</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>4510100</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>4205700</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>4584300</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>4132100</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2608000</v>
+      </c>
+      <c r="E9" s="3">
         <v>2360000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2858000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2530000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2413000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2215000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2648000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2397000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2315000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2284000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2531000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2349000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2594000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2287000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>10455000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>3079000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>3030000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2983000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>3205000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2870000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2821000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2605000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2806200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2657700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2444800</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1900300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2164400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1936600</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1960700</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1865300</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1164900</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>2162600</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>2163900</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>2051800</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>2246600</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>1991400</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>2027800</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>1871400</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>2084300</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>1846100</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>3657000</v>
+      </c>
+      <c r="E10" s="3">
         <v>3591000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>3980000</v>
-      </c>
-      <c r="F10" s="3">
-        <v>3523000</v>
       </c>
       <c r="G10" s="3">
         <v>3523000</v>
       </c>
       <c r="H10" s="3">
+        <v>3523000</v>
+      </c>
+      <c r="I10" s="3">
         <v>3526000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>3890000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3401000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>3428000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>3512000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>3874000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>3275000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>3318000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>3662000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>16188000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>4584000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>4721000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>4705000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>4943000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>4359000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>4397000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>4253000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>3954100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>3225500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>2852600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>2442800</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>2703900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>2441400</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>2483800</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>2354900</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1354100</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>2690500</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>2817100</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>2643600</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>2839100</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>2536800</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>2482300</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>2334300</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>2500000</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>2286000</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1234,130 +1247,134 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>412000</v>
+      </c>
+      <c r="E12" s="3">
         <v>387000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>438000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>378000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>403000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>379000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>442000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>383000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>391000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>368000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>407000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>362000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>361000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>373000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>1528000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>420000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>431000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>441000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>495000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>441000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>426000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>380000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>395800</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>342600</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>322600</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>287000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>293800</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>282600</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>282100</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>267500</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>147600</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>301200</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>311700</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>298700</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>298900</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>279200</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>283300</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>501200</v>
       </c>
-      <c r="AO12" s="3">
+      <c r="AP12" s="3">
         <v>268000</v>
       </c>
-      <c r="AP12" s="3">
+      <c r="AQ12" s="3">
         <v>241100</v>
       </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1478,53 +1495,56 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>115000</v>
+      </c>
+      <c r="E14" s="3">
         <v>94000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>14000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>116000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>476000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>96000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>150000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>119000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>59000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>62000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>311000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>48000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>17000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-22000</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
@@ -1535,46 +1555,46 @@
         <v>0</v>
       </c>
       <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>96000</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
       <c r="W14" s="3">
         <v>0</v>
       </c>
       <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
         <v>-13000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>25600</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
       <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
         <v>-454600</v>
       </c>
-      <c r="AB14" s="3" t="s">
+      <c r="AC14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>7000</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
-      </c>
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-      <c r="AF14" s="3" t="s">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AG14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH14" s="3" t="s">
-        <v>10</v>
+      <c r="AH14" s="3">
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="s">
         <v>10</v>
@@ -1582,71 +1602,74 @@
       <c r="AJ14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AK14" s="3">
-        <v>0</v>
+      <c r="AK14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AL14" s="3">
         <v>0</v>
       </c>
-      <c r="AM14" s="3" t="s">
-        <v>10</v>
+      <c r="AM14" s="3">
+        <v>0</v>
       </c>
       <c r="AN14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AO14" s="3">
-        <v>0</v>
+      <c r="AO14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AP14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ14" s="3">
         <v>178800</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>659000</v>
+      </c>
+      <c r="E15" s="3">
         <v>627000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>623000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>622000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>611000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>591000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>595000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>591000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>580000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>586000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>558000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>533000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>540000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>535000</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1722,8 +1745,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1763,252 +1789,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>5026000</v>
+      </c>
+      <c r="E17" s="3">
         <v>4586000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>5322000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>4797000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>4742000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>4450000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>5026000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>4619000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4575000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4458000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4894000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4438000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4747000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4430000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>19107000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>5648000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>5546000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>5516000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>6090000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>5920000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>5213000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>4848000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>5184600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>4795600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3998200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>3645600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3914000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>3601700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>3632800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3500500</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1905100</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>4022400</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>4113500</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>3952400</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>4148200</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>3769000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>3833400</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>3588700</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>3855700</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>3611800</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1239000</v>
+      </c>
+      <c r="E18" s="3">
         <v>1365000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1516000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1256000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1194000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1291000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1512000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1179000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1168000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1338000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1511000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1186000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1165000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1519000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>7536000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2015000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2205000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2172000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>2058000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1309000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>2005000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>2010000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1575700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1087600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1299200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>697500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>954300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>776300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>811700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>719700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>613900</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>830700</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>867500</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>743000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>937500</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>759200</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>676700</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>617000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>728600</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>520300</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2051,19 +2084,20 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E20" s="3">
+      <c r="E20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F20" s="3">
         <v>87000</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>10</v>
@@ -2095,574 +2129,589 @@
       <c r="P20" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R20" s="3">
         <v>-186000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-42000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-85000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-19000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>83000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>140000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>100000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>131000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>38100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>10600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>61000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>64700</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>34300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>31200</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>20800</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>11800</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>11900</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>10800</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>9200</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>83300</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>10500</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>8800</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>8500</v>
-      </c>
-      <c r="AO20" s="3">
-        <v>100</v>
       </c>
       <c r="AP20" s="3">
         <v>100</v>
       </c>
+      <c r="AQ20" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1898000</v>
+      </c>
+      <c r="E21" s="3">
         <v>1992000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>2052000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1878000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1805000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1882000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2107000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1770000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1748000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1924000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2069000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1719000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1705000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>2054000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>9572000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>2513000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>2672000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>2718000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>2728000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>2003000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>2630000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>2643000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>2122400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1589700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1776600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1056300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1221600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1138300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1173700</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1068900</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>956500</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1164100</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1212900</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1073000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1338900</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>1081100</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>988700</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>931100</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>1034300</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>797600</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>107000</v>
+      </c>
+      <c r="E22" s="3">
         <v>63000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>55000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>67000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>71000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>72000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>61000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>87000</v>
-      </c>
-      <c r="K22" s="3">
-        <v>65000</v>
       </c>
       <c r="L22" s="3">
         <v>65000</v>
       </c>
       <c r="M22" s="3">
+        <v>65000</v>
+      </c>
+      <c r="N22" s="3">
         <v>85000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>70000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>65000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>66000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>204000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>42000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>51000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>54000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>56000</v>
-      </c>
-      <c r="V22" s="3">
-        <v>62000</v>
       </c>
       <c r="W22" s="3">
         <v>62000</v>
       </c>
       <c r="X22" s="3">
+        <v>62000</v>
+      </c>
+      <c r="Y22" s="3">
         <v>58000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>72300</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>76700</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>78600</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>47400</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>43800</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>24000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>19700</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>20500</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>13300</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>41300</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>43200</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>39100</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>41800</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>39900</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>40700</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>40300</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>32300</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>43700</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1078000</v>
+      </c>
+      <c r="E23" s="3">
         <v>1235000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1373000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1076000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>655000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1129000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1315000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>977000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1083000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1271000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1232000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1147000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1142000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1523000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>7146000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1931000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>2069000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>2099000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>2085000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1387000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>2043000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>2083000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1541500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1021500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1220900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>711100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>975200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>786600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>823200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>720000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>612400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>801300</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>835100</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>713100</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>979000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>729800</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>644800</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>585200</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>696400</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>476700</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>208000</v>
+      </c>
+      <c r="E24" s="3">
         <v>206000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>190000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>168000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>100000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>175000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>229000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>159000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>176000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>183000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>111000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>207000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>222000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>283000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>818000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>359000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>389000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>374000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>297000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>229000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>344000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>381000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>301400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>138000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>293600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>116000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>182600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>155900</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>146800</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>387700</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>117200</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>137600</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>161300</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>146500</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>122400</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>157700</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>87500</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>101400</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>-50600</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>74100</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2783,252 +2832,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>870000</v>
+      </c>
+      <c r="E26" s="3">
         <v>1029000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1183000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>908000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>555000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>954000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1086000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>818000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>907000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1088000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1121000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>940000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>920000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1240000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>6328000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1572000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1680000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1725000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1788000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1158000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1699000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1702000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1240100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>883500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>927300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>595100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>792600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>630700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>676400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>332300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>495200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>663700</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>673800</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>566600</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>856600</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>572100</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>557300</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>483800</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>747000</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>402600</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>870000</v>
+      </c>
+      <c r="E27" s="3">
         <v>1029000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1197000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>908000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>555000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>954000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1086000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>818000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>907000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1088000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1079000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1129000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1106000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1429000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>6222000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1551000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1658000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1684000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1747000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1117000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1658000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1661000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1199400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>842400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>892700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>575500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>779300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>605200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>653700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>325800</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>495200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>663700</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>673800</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>566600</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>856600</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>572100</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>557300</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>483800</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>747000</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>402600</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3149,8 +3207,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3158,11 +3219,11 @@
         <v>0</v>
       </c>
       <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
         <v>14000</v>
       </c>
-      <c r="F29" s="3">
-        <v>0</v>
-      </c>
       <c r="G29" s="3">
         <v>0</v>
       </c>
@@ -3182,41 +3243,41 @@
         <v>0</v>
       </c>
       <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
         <v>-42000</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>189000</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>186000</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>210000</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>881000</v>
       </c>
-      <c r="R29" s="3">
-        <v>0</v>
-      </c>
       <c r="S29" s="3">
         <v>0</v>
       </c>
-      <c r="T29" s="3" t="s">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="U29" s="3">
-        <v>0</v>
-      </c>
       <c r="V29" s="3">
         <v>0</v>
       </c>
       <c r="W29" s="3">
+        <v>0</v>
+      </c>
+      <c r="X29" s="3">
         <v>86000</v>
       </c>
-      <c r="X29" s="3">
-        <v>0</v>
-      </c>
       <c r="Y29" s="3">
         <v>0</v>
       </c>
@@ -3230,23 +3291,23 @@
         <v>0</v>
       </c>
       <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="3">
         <v>482300</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>37300</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>54900</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>1500</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>251600</v>
       </c>
-      <c r="AH29" s="3">
-        <v>0</v>
-      </c>
       <c r="AI29" s="3">
         <v>0</v>
       </c>
@@ -3263,16 +3324,19 @@
         <v>0</v>
       </c>
       <c r="AN29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO29" s="3">
         <v>22300</v>
       </c>
-      <c r="AO29" s="3">
-        <v>0</v>
-      </c>
       <c r="AP29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ29" s="3">
         <v>-11000</v>
       </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3393,8 +3457,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3515,19 +3582,22 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E32" s="3">
+      <c r="E32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F32" s="3">
         <v>-87000</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>10</v>
@@ -3559,208 +3629,214 @@
       <c r="P32" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R32" s="3">
         <v>186000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>42000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>85000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>19000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-83000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-140000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-100000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-131000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-38100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-10600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-61000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-64700</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-34300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-31200</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-20800</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-11800</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-11900</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-10800</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-9200</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-83300</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-10500</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-8800</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-8500</v>
-      </c>
-      <c r="AO32" s="3">
-        <v>-100</v>
       </c>
       <c r="AP32" s="3">
         <v>-100</v>
       </c>
+      <c r="AQ32" s="3">
+        <v>-100</v>
+      </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>870000</v>
+      </c>
+      <c r="E33" s="3">
         <v>1029000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1197000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>908000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>555000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>954000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1086000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>818000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>907000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1088000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1079000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1129000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1106000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1450000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>7103000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1551000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1658000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1684000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1747000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1117000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1744000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1661000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1199400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>842400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>892700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>575500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1261600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>642500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>708600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>327300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>746800</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>663700</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>673800</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>566600</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>856600</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>572100</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>557300</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>506100</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>747000</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>391600</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3881,257 +3957,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>870000</v>
+      </c>
+      <c r="E35" s="3">
         <v>1029000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1197000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>908000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>555000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>954000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1086000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>818000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>907000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1088000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1079000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1129000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1106000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1450000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>7103000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1551000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1658000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1684000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1747000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1117000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1744000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1661000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1199400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>842400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>892700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>575500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1261600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>642500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>708600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>327300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>746800</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>663700</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>673800</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>566600</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>856600</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>572100</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>557300</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>506100</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>747000</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>391600</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46199</v>
+      </c>
+      <c r="E38" s="2">
         <v>46108</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45835</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45744</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45562</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45471</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45380</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45198</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44743</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44652</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44470</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44379</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44288</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44106</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44015</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43924</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43735</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43644</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43553</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43371</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43280</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43189</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43007</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4174,8 +4259,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4218,130 +4304,134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4348000</v>
+      </c>
+      <c r="E41" s="3">
         <v>5701000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>4615000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1528000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2957000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1993000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2078000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2627000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2374000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>7031000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>5864000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>12277000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>8575000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>7379000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>5995000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>5150000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>3984000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>3717000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2586000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2552000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>7322000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>6330000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>6035000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>5687700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>5539300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>4367700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>19912300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>14252100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>5433600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>3910000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>787800</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>776200</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>904000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>1045700</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>630300</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>648600</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>726400</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>803900</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>963700</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>971400</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4462,252 +4552,261 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4963000</v>
+      </c>
+      <c r="E43" s="3">
         <v>4758000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>4902000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3755000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>4516000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>4314000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>4390000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>4097000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3911000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3379000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>4637000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>4264000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>4273000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>4397000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>5008000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>4484000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>4615000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>4496000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>4706000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>4282000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>4197000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>4026000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>4110000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>3562700</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>3465400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>3553300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>3268400</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>3544100</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>3566600</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>3506200</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>3571600</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>3420100</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>3394600</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>3364700</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>3521800</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>3254600</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>3214800</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>3034900</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>3186100</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>3081800</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>3260000</v>
+      </c>
+      <c r="E44" s="3">
         <v>2608000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2489000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2674000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2689000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2532000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2330000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2678000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2671000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2645000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2594000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>3024000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>3183000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>3383000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>3110000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>3236000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>3257000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>3072000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>2767000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>2737000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>2547000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>2424000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>2292000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>2421700</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>2592900</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>2575000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1628300</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>2023700</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>2055900</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>2027900</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1910100</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>2029400</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>1980500</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>1949100</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>1840800</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>1892300</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>1791700</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>1764900</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>1709400</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>1712200</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4750,208 +4849,214 @@
       <c r="P45" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="Q45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R45" s="3">
         <v>1770000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1380000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1373000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1385000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1589000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1205000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1326000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1232000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1365000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>869100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>746200</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>646600</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>787600</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>533800</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>547600</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>636300</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>824300</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>604800</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>634000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>715600</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>857100</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>464700</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>523700</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>715200</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>805900</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>727800</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>13381000</v>
+      </c>
+      <c r="E46" s="3">
         <v>13935000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>12756000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>9606000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>10999000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>9525000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>9497000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>10060000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>9609000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>14372000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>13937000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>21205000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>17461000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>16532000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>15883000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>14250000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>13229000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>12670000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>11648000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>10776000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>15392000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>14012000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>13802000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>12541200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>12343800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>11142600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>25596600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>20353700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>11603700</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>10080400</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>7093800</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>6830500</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>6913100</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>7075100</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>6850000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>6260200</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>6256600</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>6318900</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>6665100</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>6493200</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4979,24 +5084,24 @@
       <c r="K47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L47" s="3">
+      <c r="L47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M47" s="3">
         <v>1000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>5000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>4000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>7000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>9000</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
-      </c>
       <c r="R47" s="3">
         <v>0</v>
       </c>
@@ -5027,297 +5132,306 @@
       <c r="AA47" s="3">
         <v>0</v>
       </c>
-      <c r="AB47" s="3" t="s">
+      <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>33700</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>35700</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>36400</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>36800</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>38300</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>40300</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>41500</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>43200</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>45400</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>190700</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>195400</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>177900</v>
-      </c>
-      <c r="AO47" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AP47" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AQ47" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>7025000</v>
+      </c>
+      <c r="E48" s="3">
         <v>6668000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>6745000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>6576000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>6409000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>6210000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>6074000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>6043000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5743000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>5662000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>5605000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5302000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5176000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>5165000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>4957000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>4684000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>4794000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>4815000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>4831000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>4620000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>4378000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>4211000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>4204000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>3958300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>3842900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>3815500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>3065700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>3475700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>3466500</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>3451000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>2511200</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>2462300</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>2492900</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>2475900</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>2454600</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>2424900</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>2422800</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>2408700</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>2354000</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>2255100</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>68772000</v>
+      </c>
+      <c r="E49" s="3">
         <v>59931000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>60968000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>61045000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>61620000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>60542000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>59065000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>62027000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>60350000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>60734000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>62354000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>57941000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>58893000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>59832000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>60052000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>58215000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>60183000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>62809000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>64027000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>64612000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>56107000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>55273000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>56702000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>55123900</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>53671600</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>52238100</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>32462200</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>36870700</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>37498600</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>37543300</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>37579100</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>37849400</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>38102400</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>37018900</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>36805700</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>36477100</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>36273500</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>35831800</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>35644900</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>31888800</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5438,8 +5552,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5560,130 +5677,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3189000</v>
+      </c>
+      <c r="E52" s="3">
         <v>3010000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>465000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2670000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2592000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2839000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>614000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2485000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2853000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2633000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>682000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3282000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3365000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3502000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>3458000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>3881000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>3600000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>3098000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>2678000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>2490000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>2150000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1930000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1453000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1267300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1410100</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1734100</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>923400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>795300</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>716800</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>662900</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>610100</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>537000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>505900</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>532100</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>492900</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>498400</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>498500</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>507800</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>631300</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>660400</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5804,130 +5927,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>92367000</v>
+      </c>
+      <c r="E54" s="3">
         <v>83544000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>83464000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>79897000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>81620000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>79116000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>77542000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>80615000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>78555000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>83402000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>84488000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>87734000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>84902000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>85040000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>84350000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>81030000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>81806000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>83392000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>83184000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>82498000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>78027000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>75426000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>76161000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>72890700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>71268400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>68930300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>62081600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>61531100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>53322000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>51774400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>47832500</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>47719500</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>48055800</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>47145200</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>46648600</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>45851300</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>45646800</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>45245100</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>45295300</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>41297500</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5970,8 +6099,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6014,275 +6144,282 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1822000</v>
+      </c>
+      <c r="E57" s="3">
         <v>1790000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1844000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1698000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1725000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1722000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1753000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1596000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1645000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1679000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1766000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1894000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1956000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2081000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2296000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2191000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2419000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2357000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2569000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2133000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1967000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1989000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2049000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1678300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1598600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1748300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1514400</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1606800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1664100</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1676200</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1712800</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1569600</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1587000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>1579000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>1509900</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>1501800</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>1427000</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>1402200</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>1485000</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>1354500</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1411000</v>
+      </c>
+      <c r="E58" s="3">
         <v>923000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>201000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>23000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>502000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>501000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>678000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1200000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>701000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1746000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1875000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2547000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1590000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1571000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>591000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>705000</v>
-      </c>
-      <c r="S58" s="3">
-        <v>10000</v>
       </c>
       <c r="T58" s="3">
         <v>10000</v>
       </c>
       <c r="U58" s="3">
+        <v>10000</v>
+      </c>
+      <c r="V58" s="3">
         <v>8000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>7000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>23000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>10000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>11000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>19700</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>17200</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>3234300</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>212400</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1068600</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>153700</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>36600</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>51800</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>59800</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>175100</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>98700</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>194700</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>182200</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>169500</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>2221000</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>2594800</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>809100</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E59" s="3">
         <v>6000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3328000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>44000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>86000</v>
       </c>
-      <c r="H59" s="3" t="s">
+      <c r="I59" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3025000</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>10</v>
@@ -6290,11 +6427,11 @@
       <c r="L59" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M59" s="3">
+      <c r="M59" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N59" s="3">
         <v>3294000</v>
-      </c>
-      <c r="N59" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="O59" s="3" t="s">
         <v>10</v>
@@ -6302,452 +6439,464 @@
       <c r="P59" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="Q59" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R59" s="3">
         <v>5502000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>5106000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>5127000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>5180000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>5563000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>5117000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>4835000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>4825000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>5342000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>4340400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>3984100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>3483000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>3205300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>3258600</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>3190200</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>2920000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>3076900</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>2835900</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>2843300</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>2765200</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>3087700</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>2703500</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>2606100</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>2379900</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>2794200</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>2599800</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>8105000</v>
+      </c>
+      <c r="E60" s="3">
         <v>7460000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>6807000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>6324000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>6792000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>6645000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>6798000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>7339000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>6701000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>7778000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>8274000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>9367000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>8404000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>8730000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>8389000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>8002000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>7556000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>7547000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>8140000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>7257000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>6825000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>6824000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>7402000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>6038400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>5599900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>8465600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>4932100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>5934000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>5008000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>4632800</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>4841500</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>4465300</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>4605400</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>4442900</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>4792300</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>4387500</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>4202600</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>6003100</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>6874000</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>4763400</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>26447000</v>
+      </c>
+      <c r="E61" s="3">
         <v>18761000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>19495000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>18133000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>18053000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>17076000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>16468000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>17624000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>17509000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>17517000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>17661000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>20613000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>19385000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>19361000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>19086000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>18542000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>20052000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>21768000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>22168000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>23591000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>20400000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>20267000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>21193000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>21806100</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>22370000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>22737200</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>21516700</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>16536200</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>10144400</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>9458200</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>9688500</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>10558000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>11145600</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>10410700</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>10327400</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>10726800</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>11422500</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>9729300</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>9674200</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>7503100</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>5223000</v>
+      </c>
+      <c r="E62" s="3">
         <v>4366000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>3782000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>4360000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>4433000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>4538000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3934000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>4347000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>4443000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>4660000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>4270000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>5339000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>5389000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>5463000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>6785000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>7493000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>7597000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>7715000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>7699000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>8189000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>8036000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>7905000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>7789000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>7073700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>7025600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>6661100</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>5350900</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>5865300</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>5956400</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>6114700</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>5075800</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>5011000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>5080400</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>5089800</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>5161100</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>5356400</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>5426500</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>5721600</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>5670300</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>5766600</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6868,8 +7017,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6990,8 +7142,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7112,130 +7267,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>39775000</v>
+      </c>
+      <c r="E66" s="3">
         <v>30587000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>30923000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>28817000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>29278000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>28259000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>27992000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>29310000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>28653000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>29955000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>30998000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>35319000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>33178000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>33554000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>34268000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>34045000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>35212000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>37036000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>38017000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>39047000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>35271000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>35007000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>36395000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>34929700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>35006700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>37875200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>31811000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>29028800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>21120800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>20217800</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>19618100</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>20046100</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>20843500</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>19955300</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>20290400</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>20475900</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>21056800</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>21459300</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>22292500</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>18105900</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7278,8 +7439,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7400,8 +7562,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7522,8 +7687,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7564,7 +7732,7 @@
         <v>0</v>
       </c>
       <c r="P70" s="3">
-        <v>1668000</v>
+        <v>0</v>
       </c>
       <c r="Q70" s="3">
         <v>1668000</v>
@@ -7576,7 +7744,7 @@
         <v>1668000</v>
       </c>
       <c r="T70" s="3">
-        <v>3268000</v>
+        <v>1668000</v>
       </c>
       <c r="U70" s="3">
         <v>3268000</v>
@@ -7594,13 +7762,13 @@
         <v>3268000</v>
       </c>
       <c r="Z70" s="3">
-        <v>3267700</v>
+        <v>3268000</v>
       </c>
       <c r="AA70" s="3">
         <v>3267700</v>
       </c>
       <c r="AB70" s="3">
-        <v>1599600</v>
+        <v>3267700</v>
       </c>
       <c r="AC70" s="3">
         <v>1599600</v>
@@ -7615,7 +7783,7 @@
         <v>1599600</v>
       </c>
       <c r="AG70" s="3">
-        <v>0</v>
+        <v>1599600</v>
       </c>
       <c r="AH70" s="3">
         <v>0</v>
@@ -7644,8 +7812,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7766,130 +7937,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>48226000</v>
+      </c>
+      <c r="E72" s="3">
         <v>47637000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>46891000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>45920000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>45239000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>44913000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>44188000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>43296000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>42673000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>41962000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>41074000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>42272000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>41344000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>40437000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>39205000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>37177000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>35808000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>34332000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>32827000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>31231000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>30264000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>28670000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>27159000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>26087800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>25373500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>24608600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>24166300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>26481200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>25955000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>25368500</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>25163000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>24528700</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>23977200</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>23415400</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>22806100</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>22047100</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>21572300</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>21112400</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>20703500</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>20043100</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8010,8 +8187,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8132,8 +8312,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8254,130 +8437,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>52581000</v>
+      </c>
+      <c r="E76" s="3">
         <v>52949000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>52534000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>51071000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>52334000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>50849000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>49543000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>51299000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>49897000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>53442000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>53486000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>52407000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>51716000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>49810000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>48414000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>45317000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>44926000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>43088000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>41899000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>40183000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>39488000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>37151000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>36498000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>34693300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>32994000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>29455500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>28671000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>30902700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>30601600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>29957000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>28214400</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>27673400</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>27212300</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>27189900</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>26358200</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>25375400</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>24590000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>23785800</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>23002800</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>23191600</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8498,257 +8687,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46199</v>
+      </c>
+      <c r="E80" s="2">
         <v>46108</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45835</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45744</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45562</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45471</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45380</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45198</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44743</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44652</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44470</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44379</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44288</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44106</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44015</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43924</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43735</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43644</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43553</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43371</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43280</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43189</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43007</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>870000</v>
+      </c>
+      <c r="E81" s="3">
         <v>1029000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1197000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>908000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>555000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>954000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1086000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>818000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>907000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1088000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1079000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1129000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1106000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1450000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>7103000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1551000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1658000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1684000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1747000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1117000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1744000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1661000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1199400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>842400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>892700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>575500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1261600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>642500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>708600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>327300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>746800</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>663700</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>673800</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>566600</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>856600</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>572100</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>557300</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>506100</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>747000</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>391600</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8791,43 +8989,44 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>185000</v>
+      </c>
+      <c r="E83" s="3">
         <v>181000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>187000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>177000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>178000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>179000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>178000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>166000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>168000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>163000</v>
       </c>
-      <c r="M83" s="3" t="s">
+      <c r="N83" s="3" t="s">
         <v>10</v>
-      </c>
-      <c r="N83" s="3">
-        <v>179000</v>
       </c>
       <c r="O83" s="3">
         <v>179000</v>
@@ -8836,85 +9035,88 @@
         <v>179000</v>
       </c>
       <c r="Q83" s="3">
+        <v>179000</v>
+      </c>
+      <c r="R83" s="3">
         <v>2222000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>540000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>552000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>565000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>587000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>554000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>525000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>502000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>508600</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>491500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>477100</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>297800</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>202600</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>327700</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>330800</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>328400</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>330800</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>321500</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>334600</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>320800</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>318100</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>311400</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>303200</v>
-      </c>
-      <c r="AN83" s="3">
-        <v>305600</v>
       </c>
       <c r="AO83" s="3">
         <v>305600</v>
       </c>
       <c r="AP83" s="3">
+        <v>305600</v>
+      </c>
+      <c r="AQ83" s="3">
         <v>191600</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9035,8 +9237,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9157,8 +9362,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9279,8 +9487,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9401,8 +9612,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9523,130 +9737,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1534000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1322000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2117000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1662000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1338000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1299000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2019000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1513000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1417000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1739000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1619000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1672000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1926000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1947000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>8519000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>2010000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>2000000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1968000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>2333000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>2034000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>2120000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1871000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>2221300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1722700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1445000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>819000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1111200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>965600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1171500</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>703300</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1237600</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>919500</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>1036000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>828900</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>834700</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>1072400</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>1010500</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>560200</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>649000</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>818200</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9689,130 +9909,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-269000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-237000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-371000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-292000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-248000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-245000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-516000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-298000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-287000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-291000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-434000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-354000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-329000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-266000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-329000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-277000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-296000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-250000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-420000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-318000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-305000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-251000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-315800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-187300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-155400</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-132500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-117100</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-181900</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-180800</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-155700</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-214400</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-149600</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-153800</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-137900</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-173800</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-139300</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-147900</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-158600</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-167500</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>186300</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9933,8 +10157,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10055,130 +10282,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-10147000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-249000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-384000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-312000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-258000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-242000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-694000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-606000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-360000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-321000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-6017000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-329000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-431000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-304000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-2234000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-515000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-400000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-503000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-879000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-10048000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1067000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-993000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-581300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-328400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>539300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-20868600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-266100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-244600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-228900</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-498500</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-297400</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-286700</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-2242600</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-122700</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-315500</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-155000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-209200</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-163700</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-4923500</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-153600</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10221,43 +10454,44 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>226000</v>
+        <v>283000</v>
       </c>
       <c r="E96" s="3">
         <v>226000</v>
       </c>
       <c r="F96" s="3">
-        <v>229000</v>
+        <v>226000</v>
       </c>
       <c r="G96" s="3">
         <v>229000</v>
       </c>
       <c r="H96" s="3">
+        <v>229000</v>
+      </c>
+      <c r="I96" s="3">
         <v>194000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>195000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>196000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>200000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>177000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>200000</v>
-      </c>
-      <c r="N96" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="O96" s="3" t="s">
         <v>10</v>
@@ -10265,17 +10499,17 @@
       <c r="P96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="Q96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R96" s="3">
         <v>-818000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-204000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-220000</v>
-      </c>
-      <c r="T96" s="3">
-        <v>-191000</v>
       </c>
       <c r="U96" s="3">
         <v>-191000</v>
@@ -10287,64 +10521,67 @@
         <v>-191000</v>
       </c>
       <c r="X96" s="3">
+        <v>-191000</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-169000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-169600</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-162300</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-145000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-138100</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-141700</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-151100</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-121700</v>
-      </c>
-      <c r="AF96" s="3">
-        <v>-112200</v>
       </c>
       <c r="AG96" s="3">
         <v>-112200</v>
       </c>
       <c r="AH96" s="3">
+        <v>-112200</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-111900</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-111800</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-97500</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-97300</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-97100</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-97300</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-86600</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-86500</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-110500</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10465,8 +10702,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10587,8 +10827,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10709,370 +10952,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>7273000</v>
+      </c>
+      <c r="E100" s="3">
         <v>46000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1322000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-2781000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-247000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1255000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1692000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-845000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-5715000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-133000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2246000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>2443000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-208000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-262000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-2570000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-230000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1160000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-274000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1422000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>3305000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-139000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-449000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-1419700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-1319800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-888000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>4633500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>4755400</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>8127700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>605000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>2877800</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-915100</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-732700</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>1172100</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-321700</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-553900</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-1028900</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-925000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-590700</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>4347000</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-3778400</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>131000</v>
+      </c>
+      <c r="E101" s="3">
         <v>113000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-182000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>191000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>1000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-118000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>231000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-84000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-91000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>3000</v>
       </c>
-      <c r="M101" s="3" t="s">
+      <c r="N101" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-99000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-173000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-60000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-306000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-99000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-173000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-60000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>2000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-61000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>78000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-134000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>127300</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>73900</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>75300</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-128500</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>59700</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-30200</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-24000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>39600</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-13500</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-27900</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-107200</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>30900</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>16400</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>33700</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>46200</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>34400</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-80200</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>-12400</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1353000</v>
+      </c>
+      <c r="E102" s="3">
         <v>1086000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>3087000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1429000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>964000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-85000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-549000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>253000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-4657000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1167000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-6413000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>3702000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1196000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1384000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>3409000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1166000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>267000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>1131000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>34000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-4770000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>992000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>295000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>347600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>148400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>1171600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-15544600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>5660200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>8818500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>1523600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>3122200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>11600</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-127800</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-141700</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>415400</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-18300</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-77800</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-77500</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-159800</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-7700</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-3126200</v>
       </c>
     </row>
